--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_vol/post_rank_positive_return/staggered_10d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_20/return_vol/post_rank_positive_return/staggered_10d/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="annual_metrics" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$H$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'annual_metrics'!$A$1:$N$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,17 +462,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -488,30 +494,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>基准收益</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>超额收益</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>年化波动</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>跟踪误差</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sharpe</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Sortino</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>信息比率</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>策略最大回撤</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>基准最大回撤</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>超额最大回撤</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Calmar</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>年化换手率（单边）</t>
         </is>
@@ -527,21 +563,39 @@
         <v>0.03306288545231961</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>-0.02176047699359285</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.05604288229678334</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0.2644937697959646</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="F2" s="3" t="n">
+        <v>0.2188335511513214</v>
+      </c>
+      <c r="G2" s="4" t="n">
         <v>0.2142286085226595</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="H2" s="4" t="n">
         <v>0.3096361127497805</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="I2" s="4" t="n">
+        <v>0.3668274030610481</v>
+      </c>
+      <c r="J2" s="3" t="n">
         <v>0.183675555169607</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="K2" s="3" t="n">
+        <v>0.1506490308477421</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.1771750755244483</v>
+      </c>
+      <c r="M2" s="4" t="n">
         <v>0.2038491611284062</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="N2" s="5" t="n">
         <v>16.90525098693649</v>
       </c>
     </row>
@@ -555,21 +609,39 @@
         <v>-0.2442781587015052</v>
       </c>
       <c r="C3" s="3" t="n">
+        <v>-0.2255774308756096</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>-0.02414796336196312</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>0.214180200559824</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="F3" s="3" t="n">
+        <v>0.1474798474382547</v>
+      </c>
+      <c r="G3" s="4" t="n">
         <v>-1.323115647244854</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="H3" s="4" t="n">
         <v>-1.672314939969103</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="I3" s="4" t="n">
+        <v>-0.1634896883803607</v>
+      </c>
+      <c r="J3" s="3" t="n">
         <v>0.2676392673698884</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="K3" s="3" t="n">
+        <v>0.2845881262232945</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.1353163157339701</v>
+      </c>
+      <c r="M3" s="4" t="n">
         <v>-0.9452057937245564</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="N3" s="5" t="n">
         <v>16.46652952024777</v>
       </c>
     </row>
@@ -583,21 +655,39 @@
         <v>-0.140154441412745</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>-0.1141699148043651</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>-0.02933353364560898</v>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>0.1933372342583006</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="F4" s="3" t="n">
+        <v>0.1471095591478845</v>
+      </c>
+      <c r="G4" s="4" t="n">
         <v>-0.7935056971100006</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>-1.073166674407313</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="I4" s="4" t="n">
+        <v>-0.1457130702627653</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>0.2429335545712561</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="K4" s="3" t="n">
+        <v>0.2177913835362562</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.1198176705585642</v>
+      </c>
+      <c r="M4" s="4" t="n">
         <v>-0.5989414593772234</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="N4" s="5" t="n">
         <v>17.17487200689081</v>
       </c>
     </row>
@@ -611,21 +701,39 @@
         <v>0.04879742578471125</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>0.1298071537204202</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-0.0717022614602365</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>0.2416984032908745</v>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>0.2622998536123457</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0.4439666370763339</v>
-      </c>
       <c r="F5" s="3" t="n">
+        <v>0.120572437658359</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>0.2622998536123451</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>0.4439666370763329</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>-0.6175328352206</v>
+      </c>
+      <c r="J5" s="3" t="n">
         <v>0.2381345207259477</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="K5" s="3" t="n">
+        <v>0.1515696200238076</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.1939256530764825</v>
+      </c>
+      <c r="M5" s="4" t="n">
         <v>0.2135948158707278</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="N5" s="5" t="n">
         <v>17.68457837083016</v>
       </c>
     </row>
@@ -636,57 +744,93 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.280676296625461</v>
+        <v>0.2806762966254612</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.2249508028398604</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1.187520601831599</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1.694729458154227</v>
+        <v>0.2243203183030871</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.04603041988266554</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0.2249508028398605</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1392517858567552</v>
+        <v>0.1188926725410113</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>2.100256390285763</v>
-      </c>
-      <c r="H6" s="5" t="n">
+        <v>1.1875206018316</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>1.694729458154228</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0.4879475991878505</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.1392517858567551</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0.1188658802983931</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.07457283967187178</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>2.100256390285766</v>
+      </c>
+      <c r="N6" s="5" t="n">
         <v>18.42359427441254</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>2026年截至07-31</t>
+          <t>2026年截至07-30</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1412638060309686</v>
+        <v>0.1401888738437691</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.3321758860276521</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.8424560874950847</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1.173970641159872</v>
+        <v>-0.01504143451691176</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.1576008512444846</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.3333858596132552</v>
       </c>
       <c r="F7" s="3" t="n">
+        <v>0.1981944011349824</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.8406408338843669</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>1.171471322949888</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>1.49641731547346</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>0.2096192312883755</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>1.291319054422642</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>16.42699665380146</v>
+      <c r="K7" s="3" t="n">
+        <v>0.127969093077366</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.1227018529079889</v>
+      </c>
+      <c r="M7" s="4" t="n">
+        <v>1.291410908299064</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>16.42168427285912</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:N7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>